--- a/test_fee_transactions.xlsx
+++ b/test_fee_transactions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,7 +452,7 @@
         <v>EUR</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-02-01</v>
+        <v>2025-01-15</v>
       </c>
     </row>
     <row r="5">
@@ -480,7 +480,7 @@
         <v>GBP</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-02-15</v>
+        <v>2025-01-20</v>
       </c>
     </row>
     <row r="7">
@@ -494,7 +494,7 @@
         <v>USD</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-03-01</v>
+        <v>2025-01-25</v>
       </c>
     </row>
     <row r="8">
@@ -508,7 +508,7 @@
         <v>EUR</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-01-25</v>
+        <v>2025-01-10</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         <v>EUR</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-02-10</v>
+        <v>2025-01-20</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         <v>USD</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-03-05</v>
+        <v>2025-01-25</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         <v>JPY</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-01-30</v>
+        <v>2025-01-15</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>JPY</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-02-20</v>
+        <v>2025-01-20</v>
       </c>
     </row>
     <row r="13">
@@ -578,12 +578,26 @@
         <v>USD</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-03-10</v>
+        <v>2025-01-25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3099</v>
+      </c>
+      <c r="B14">
+        <v>500</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CHF</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2025-02-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
   </ignoredErrors>
 </worksheet>
 </file>